--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36AC4C5-BC7D-4781-A206-D210606BFA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B8E681-41C4-4E0A-8E7B-EB4045BD3F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -1218,20 +1218,83 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1239,15 +1302,54 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1264,108 +1366,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1759,13 +1759,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="105" t="s">
+      <c r="A3" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="119" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="107" t="s">
+      <c r="C3" s="121" t="s">
         <v>94</v>
       </c>
       <c r="D3" s="61" t="s">
@@ -1782,9 +1782,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="105"/>
-      <c r="B4" s="108"/>
-      <c r="C4" s="107"/>
+      <c r="A4" s="119"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="121"/>
       <c r="D4" s="68" t="s">
         <v>21</v>
       </c>
@@ -1810,13 +1810,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="105" t="s">
+      <c r="A6" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="105" t="s">
+      <c r="B6" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="86" t="s">
+      <c r="C6" s="94" t="s">
         <v>77</v>
       </c>
       <c r="D6" s="68" t="s">
@@ -1833,9 +1833,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="105"/>
-      <c r="B7" s="106"/>
-      <c r="C7" s="128"/>
+      <c r="A7" s="119"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="95"/>
       <c r="D7" s="61" t="s">
         <v>101</v>
       </c>
@@ -1850,9 +1850,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="105"/>
-      <c r="B8" s="106"/>
-      <c r="C8" s="114"/>
+      <c r="A8" s="119"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="96"/>
       <c r="D8" s="68" t="s">
         <v>102</v>
       </c>
@@ -1867,15 +1867,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="105"/>
-      <c r="B9" s="106"/>
-      <c r="C9" s="86" t="s">
+      <c r="A9" s="119"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="94" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="121" t="s">
+      <c r="E9" s="87" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="64" t="s">
@@ -1892,13 +1892,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="105"/>
-      <c r="B10" s="106"/>
-      <c r="C10" s="128"/>
+      <c r="A10" s="119"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="95"/>
       <c r="D10" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="90"/>
+      <c r="E10" s="88"/>
       <c r="F10" s="70" t="s">
         <v>9</v>
       </c>
@@ -1907,9 +1907,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="105"/>
-      <c r="B11" s="106"/>
-      <c r="C11" s="114"/>
+      <c r="A11" s="119"/>
+      <c r="B11" s="120"/>
+      <c r="C11" s="96"/>
       <c r="D11" s="66" t="s">
         <v>36</v>
       </c>
@@ -1924,18 +1924,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="105"/>
-      <c r="B12" s="106"/>
-      <c r="C12" s="109" t="s">
+      <c r="A12" s="119"/>
+      <c r="B12" s="120"/>
+      <c r="C12" s="123" t="s">
         <v>95</v>
       </c>
       <c r="D12" s="61" t="s">
         <v>139</v>
       </c>
-      <c r="E12" s="116" t="s">
+      <c r="E12" s="102" t="s">
         <v>143</v>
       </c>
-      <c r="F12" s="130" t="s">
+      <c r="F12" s="99" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1943,40 +1943,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="105"/>
-      <c r="B13" s="106"/>
-      <c r="C13" s="110"/>
+      <c r="A13" s="119"/>
+      <c r="B13" s="120"/>
+      <c r="C13" s="124"/>
       <c r="D13" s="61" t="s">
         <v>142</v>
       </c>
-      <c r="E13" s="116"/>
-      <c r="F13" s="131"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="100"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="105"/>
-      <c r="B14" s="106"/>
-      <c r="C14" s="110"/>
+      <c r="A14" s="119"/>
+      <c r="B14" s="120"/>
+      <c r="C14" s="124"/>
       <c r="D14" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="E14" s="116"/>
-      <c r="F14" s="131"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="100"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="105"/>
-      <c r="B15" s="106"/>
-      <c r="C15" s="111"/>
+      <c r="A15" s="119"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="125"/>
       <c r="D15" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="E15" s="117"/>
-      <c r="F15" s="132"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="101"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1993,13 +1993,13 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="91" t="s">
+      <c r="B17" s="112" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="86" t="s">
+      <c r="C17" s="94" t="s">
         <v>96</v>
       </c>
       <c r="D17" s="68" t="s">
@@ -2016,9 +2016,9 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="89"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="87"/>
+      <c r="A18" s="107"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="97"/>
       <c r="D18" s="61" t="s">
         <v>103</v>
       </c>
@@ -2033,9 +2033,9 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="89"/>
-      <c r="B19" s="89"/>
-      <c r="C19" s="129"/>
+      <c r="A19" s="107"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="98"/>
       <c r="D19" s="68" t="s">
         <v>79</v>
       </c>
@@ -2050,15 +2050,15 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="89"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="86" t="s">
+      <c r="A20" s="107"/>
+      <c r="B20" s="107"/>
+      <c r="C20" s="94" t="s">
         <v>141</v>
       </c>
       <c r="D20" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="121" t="s">
+      <c r="E20" s="87" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="64" t="s">
@@ -2075,13 +2075,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="89"/>
-      <c r="B21" s="89"/>
-      <c r="C21" s="128"/>
+      <c r="A21" s="107"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="95"/>
       <c r="D21" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="90"/>
+      <c r="E21" s="88"/>
       <c r="F21" s="69" t="s">
         <v>9</v>
       </c>
@@ -2090,9 +2090,9 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="89"/>
-      <c r="B22" s="89"/>
-      <c r="C22" s="128"/>
+      <c r="A22" s="107"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="95"/>
       <c r="D22" s="66" t="s">
         <v>36</v>
       </c>
@@ -2107,16 +2107,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="89"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="128"/>
+      <c r="A23" s="107"/>
+      <c r="B23" s="107"/>
+      <c r="C23" s="95"/>
       <c r="D23" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="E23" s="121" t="s">
+      <c r="E23" s="87" t="s">
         <v>143</v>
       </c>
-      <c r="F23" s="118" t="s">
+      <c r="F23" s="104" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -2124,60 +2124,60 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="89"/>
-      <c r="B24" s="89"/>
-      <c r="C24" s="128"/>
+      <c r="A24" s="107"/>
+      <c r="B24" s="107"/>
+      <c r="C24" s="95"/>
       <c r="D24" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="E24" s="89"/>
-      <c r="F24" s="119"/>
+      <c r="E24" s="107"/>
+      <c r="F24" s="105"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="89"/>
-      <c r="B25" s="89"/>
-      <c r="C25" s="128"/>
+      <c r="A25" s="107"/>
+      <c r="B25" s="107"/>
+      <c r="C25" s="95"/>
       <c r="D25" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="E25" s="89"/>
-      <c r="F25" s="119"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="105"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="89"/>
-      <c r="B26" s="89"/>
-      <c r="C26" s="128"/>
+      <c r="A26" s="107"/>
+      <c r="B26" s="107"/>
+      <c r="C26" s="95"/>
       <c r="D26" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="E26" s="89"/>
-      <c r="F26" s="119"/>
+      <c r="E26" s="107"/>
+      <c r="F26" s="105"/>
       <c r="G26" s="45"/>
       <c r="H26" s="3"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="89"/>
-      <c r="B27" s="89"/>
-      <c r="C27" s="114"/>
+      <c r="A27" s="107"/>
+      <c r="B27" s="107"/>
+      <c r="C27" s="96"/>
       <c r="D27" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="E27" s="90"/>
-      <c r="F27" s="120"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="106"/>
       <c r="G27" s="31"/>
       <c r="H27" s="1"/>
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="89"/>
-      <c r="B28" s="89"/>
+      <c r="A28" s="107"/>
+      <c r="B28" s="107"/>
       <c r="C28" s="82" t="s">
         <v>104</v>
       </c>
@@ -2195,8 +2195,8 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="90"/>
-      <c r="B29" s="90"/>
+      <c r="A29" s="88"/>
+      <c r="B29" s="88"/>
       <c r="C29" s="81" t="s">
         <v>104</v>
       </c>
@@ -2214,22 +2214,22 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="91" t="s">
+      <c r="A30" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="91" t="s">
+      <c r="B30" s="112" t="s">
         <v>153</v>
       </c>
-      <c r="C30" s="102" t="s">
+      <c r="C30" s="116" t="s">
         <v>151</v>
       </c>
       <c r="D30" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="E30" s="124" t="s">
+      <c r="E30" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="88" t="s">
+      <c r="F30" s="127" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="31"/>
@@ -2237,39 +2237,39 @@
       <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="89"/>
-      <c r="B31" s="89"/>
-      <c r="C31" s="103"/>
+      <c r="A31" s="107"/>
+      <c r="B31" s="107"/>
+      <c r="C31" s="117"/>
       <c r="D31" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="E31" s="124"/>
-      <c r="F31" s="89"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="107"/>
       <c r="G31" s="31"/>
       <c r="H31" s="1"/>
       <c r="I31" s="39"/>
     </row>
     <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="89"/>
-      <c r="B32" s="89"/>
-      <c r="C32" s="103"/>
+      <c r="A32" s="107"/>
+      <c r="B32" s="107"/>
+      <c r="C32" s="117"/>
       <c r="D32" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="E32" s="124"/>
-      <c r="F32" s="90"/>
+      <c r="E32" s="108"/>
+      <c r="F32" s="88"/>
       <c r="G32" s="31"/>
       <c r="H32" s="1"/>
       <c r="I32" s="39"/>
     </row>
     <row r="33" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="89"/>
-      <c r="B33" s="89"/>
-      <c r="C33" s="104"/>
+      <c r="A33" s="107"/>
+      <c r="B33" s="107"/>
+      <c r="C33" s="118"/>
       <c r="D33" s="83" t="s">
         <v>156</v>
       </c>
-      <c r="E33" s="124"/>
+      <c r="E33" s="108"/>
       <c r="F33" s="84" t="s">
         <v>9</v>
       </c>
@@ -2278,16 +2278,16 @@
       <c r="I33" s="39"/>
     </row>
     <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="89"/>
-      <c r="B34" s="89"/>
-      <c r="C34" s="102" t="s">
+      <c r="A34" s="107"/>
+      <c r="B34" s="107"/>
+      <c r="C34" s="116" t="s">
         <v>154</v>
       </c>
       <c r="D34" s="61" t="s">
         <v>157</v>
       </c>
-      <c r="E34" s="124"/>
-      <c r="F34" s="88" t="s">
+      <c r="E34" s="108"/>
+      <c r="F34" s="127" t="s">
         <v>7</v>
       </c>
       <c r="G34" s="31"/>
@@ -2295,117 +2295,117 @@
       <c r="I34" s="39"/>
     </row>
     <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="89"/>
-      <c r="B35" s="89"/>
-      <c r="C35" s="112"/>
+      <c r="A35" s="107"/>
+      <c r="B35" s="107"/>
+      <c r="C35" s="126"/>
       <c r="D35" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="E35" s="124"/>
-      <c r="F35" s="89"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="107"/>
       <c r="G35" s="31"/>
       <c r="H35" s="1"/>
       <c r="I35" s="39"/>
     </row>
     <row r="36" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="89"/>
-      <c r="B36" s="89"/>
-      <c r="C36" s="103"/>
+      <c r="A36" s="107"/>
+      <c r="B36" s="107"/>
+      <c r="C36" s="117"/>
       <c r="D36" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E36" s="124"/>
-      <c r="F36" s="89"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="107"/>
       <c r="G36" s="31"/>
       <c r="H36" s="1"/>
       <c r="I36" s="39"/>
     </row>
     <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="89"/>
-      <c r="B37" s="89"/>
-      <c r="C37" s="103"/>
+      <c r="A37" s="107"/>
+      <c r="B37" s="107"/>
+      <c r="C37" s="117"/>
       <c r="D37" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="E37" s="124"/>
-      <c r="F37" s="89"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="107"/>
       <c r="G37" s="31"/>
       <c r="H37" s="1"/>
       <c r="I37" s="39"/>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="89"/>
-      <c r="B38" s="89"/>
-      <c r="C38" s="103"/>
+      <c r="A38" s="107"/>
+      <c r="B38" s="107"/>
+      <c r="C38" s="117"/>
       <c r="D38" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="E38" s="124"/>
-      <c r="F38" s="89"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="107"/>
       <c r="G38" s="31"/>
       <c r="H38" s="1"/>
       <c r="I38" s="39"/>
     </row>
     <row r="39" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="89"/>
-      <c r="B39" s="89"/>
-      <c r="C39" s="103"/>
+      <c r="A39" s="107"/>
+      <c r="B39" s="107"/>
+      <c r="C39" s="117"/>
       <c r="D39" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E39" s="124"/>
-      <c r="F39" s="89"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="107"/>
       <c r="G39" s="31"/>
       <c r="H39" s="1"/>
       <c r="I39" s="39"/>
     </row>
     <row r="40" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="89"/>
-      <c r="B40" s="89"/>
-      <c r="C40" s="103"/>
-      <c r="D40" s="68" t="s">
+      <c r="A40" s="107"/>
+      <c r="B40" s="107"/>
+      <c r="C40" s="117"/>
+      <c r="D40" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="E40" s="124"/>
-      <c r="F40" s="89"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="107"/>
       <c r="G40" s="31"/>
       <c r="H40" s="1"/>
       <c r="I40" s="39"/>
     </row>
     <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="89"/>
-      <c r="B41" s="89"/>
-      <c r="C41" s="103"/>
+      <c r="A41" s="107"/>
+      <c r="B41" s="107"/>
+      <c r="C41" s="117"/>
       <c r="D41" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="E41" s="124"/>
-      <c r="F41" s="89"/>
+      <c r="E41" s="108"/>
+      <c r="F41" s="107"/>
       <c r="G41" s="31"/>
       <c r="H41" s="1"/>
       <c r="I41" s="39"/>
     </row>
     <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="89"/>
-      <c r="B42" s="89"/>
-      <c r="C42" s="103"/>
+      <c r="A42" s="107"/>
+      <c r="B42" s="107"/>
+      <c r="C42" s="117"/>
       <c r="D42" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E42" s="124"/>
-      <c r="F42" s="89"/>
+      <c r="E42" s="108"/>
+      <c r="F42" s="107"/>
       <c r="G42" s="31"/>
       <c r="H42" s="1"/>
       <c r="I42" s="39"/>
     </row>
     <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="90"/>
-      <c r="B43" s="90"/>
-      <c r="C43" s="104"/>
+      <c r="A43" s="88"/>
+      <c r="B43" s="88"/>
+      <c r="C43" s="118"/>
       <c r="D43" s="83" t="s">
         <v>156</v>
       </c>
-      <c r="E43" s="124"/>
+      <c r="E43" s="108"/>
       <c r="F43" s="85" t="s">
         <v>9</v>
       </c>
@@ -2425,13 +2425,13 @@
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="91" t="s">
+      <c r="A45" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="91" t="s">
+      <c r="B45" s="112" t="s">
         <v>163</v>
       </c>
-      <c r="C45" s="135" t="s">
+      <c r="C45" s="115" t="s">
         <v>164</v>
       </c>
       <c r="D45" s="60" t="s">
@@ -2440,7 +2440,7 @@
       <c r="E45" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F45" s="134" t="s">
+      <c r="F45" s="86" t="s">
         <v>7</v>
       </c>
       <c r="G45" s="1"/>
@@ -2448,9 +2448,9 @@
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="90"/>
-      <c r="B46" s="90"/>
-      <c r="C46" s="135"/>
+      <c r="A46" s="88"/>
+      <c r="B46" s="88"/>
+      <c r="C46" s="115"/>
       <c r="D46" s="68" t="s">
         <v>166</v>
       </c>
@@ -2465,13 +2465,13 @@
       <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="91" t="s">
+      <c r="A47" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="91" t="s">
+      <c r="B47" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="93" t="s">
+      <c r="C47" s="128" t="s">
         <v>78</v>
       </c>
       <c r="D47" s="66" t="s">
@@ -2488,16 +2488,16 @@
       <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="92"/>
-      <c r="B48" s="92"/>
-      <c r="C48" s="94"/>
+      <c r="A48" s="113"/>
+      <c r="B48" s="113"/>
+      <c r="C48" s="129"/>
       <c r="D48" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="E48" s="121" t="s">
+      <c r="E48" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="F48" s="122" t="s">
+      <c r="F48" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G48" s="31"/>
@@ -2505,22 +2505,22 @@
       <c r="I48" s="32"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="92"/>
-      <c r="B49" s="92"/>
-      <c r="C49" s="94"/>
+      <c r="A49" s="113"/>
+      <c r="B49" s="113"/>
+      <c r="C49" s="129"/>
       <c r="D49" s="59" t="s">
         <v>111</v>
       </c>
-      <c r="E49" s="90"/>
-      <c r="F49" s="127"/>
+      <c r="E49" s="88"/>
+      <c r="F49" s="111"/>
       <c r="G49" s="31"/>
       <c r="H49" s="3"/>
       <c r="I49" s="32"/>
     </row>
     <row r="50" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="92"/>
-      <c r="B50" s="92"/>
-      <c r="C50" s="95"/>
+      <c r="A50" s="113"/>
+      <c r="B50" s="113"/>
+      <c r="C50" s="92"/>
       <c r="D50" s="68" t="s">
         <v>80</v>
       </c>
@@ -2535,9 +2535,9 @@
       <c r="I50" s="32"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="92"/>
-      <c r="B51" s="92"/>
-      <c r="C51" s="100" t="s">
+      <c r="A51" s="113"/>
+      <c r="B51" s="113"/>
+      <c r="C51" s="134" t="s">
         <v>112</v>
       </c>
       <c r="D51" s="66" t="s">
@@ -2554,9 +2554,9 @@
       <c r="I51" s="32"/>
     </row>
     <row r="52" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="92"/>
-      <c r="B52" s="92"/>
-      <c r="C52" s="101"/>
+      <c r="A52" s="113"/>
+      <c r="B52" s="113"/>
+      <c r="C52" s="135"/>
       <c r="D52" s="66" t="s">
         <v>113</v>
       </c>
@@ -2571,15 +2571,15 @@
       <c r="I52" s="32"/>
     </row>
     <row r="53" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="92"/>
-      <c r="B53" s="92"/>
-      <c r="C53" s="86" t="s">
+      <c r="A53" s="113"/>
+      <c r="B53" s="113"/>
+      <c r="C53" s="94" t="s">
         <v>97</v>
       </c>
       <c r="D53" s="66" t="s">
         <v>106</v>
       </c>
-      <c r="E53" s="125" t="s">
+      <c r="E53" s="109" t="s">
         <v>105</v>
       </c>
       <c r="F53" s="77" t="s">
@@ -2592,13 +2592,13 @@
       <c r="I53" s="32"/>
     </row>
     <row r="54" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="92"/>
-      <c r="B54" s="92"/>
-      <c r="C54" s="87"/>
+      <c r="A54" s="113"/>
+      <c r="B54" s="113"/>
+      <c r="C54" s="97"/>
       <c r="D54" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="E54" s="126"/>
+      <c r="E54" s="110"/>
       <c r="F54" s="71" t="s">
         <v>9</v>
       </c>
@@ -2607,13 +2607,13 @@
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="92"/>
-      <c r="B55" s="92"/>
-      <c r="C55" s="87"/>
+      <c r="A55" s="113"/>
+      <c r="B55" s="113"/>
+      <c r="C55" s="97"/>
       <c r="D55" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="E55" s="90"/>
+      <c r="E55" s="88"/>
       <c r="F55" s="71" t="s">
         <v>9</v>
       </c>
@@ -2622,9 +2622,9 @@
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="92"/>
-      <c r="B56" s="92"/>
-      <c r="C56" s="86" t="s">
+      <c r="A56" s="113"/>
+      <c r="B56" s="113"/>
+      <c r="C56" s="94" t="s">
         <v>115</v>
       </c>
       <c r="D56" s="68" t="s">
@@ -2643,9 +2643,9 @@
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="92"/>
-      <c r="B57" s="92"/>
-      <c r="C57" s="114"/>
+      <c r="A57" s="113"/>
+      <c r="B57" s="113"/>
+      <c r="C57" s="96"/>
       <c r="D57" s="66" t="s">
         <v>117</v>
       </c>
@@ -2662,8 +2662,8 @@
       <c r="I57" s="34"/>
     </row>
     <row r="58" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="113"/>
-      <c r="B58" s="113"/>
+      <c r="A58" s="114"/>
+      <c r="B58" s="114"/>
       <c r="C58" s="78" t="s">
         <v>81</v>
       </c>
@@ -2698,13 +2698,13 @@
       <c r="I59" s="28"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="98" t="s">
+      <c r="A60" s="132" t="s">
         <v>167</v>
       </c>
-      <c r="B60" s="91" t="s">
+      <c r="B60" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="C60" s="93" t="s">
+      <c r="C60" s="128" t="s">
         <v>86</v>
       </c>
       <c r="D60" s="66" t="s">
@@ -2723,16 +2723,16 @@
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="99"/>
-      <c r="B61" s="92"/>
-      <c r="C61" s="97"/>
+      <c r="A61" s="133"/>
+      <c r="B61" s="113"/>
+      <c r="C61" s="131"/>
       <c r="D61" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="E61" s="121" t="s">
+      <c r="E61" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="F61" s="122" t="s">
+      <c r="F61" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="31"/>
@@ -2740,22 +2740,22 @@
       <c r="I61" s="32"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="99"/>
-      <c r="B62" s="92"/>
-      <c r="C62" s="97"/>
+      <c r="A62" s="133"/>
+      <c r="B62" s="113"/>
+      <c r="C62" s="131"/>
       <c r="D62" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="E62" s="90"/>
-      <c r="F62" s="123"/>
+      <c r="E62" s="88"/>
+      <c r="F62" s="90"/>
       <c r="G62" s="31"/>
       <c r="H62" s="3"/>
       <c r="I62" s="32"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="99"/>
-      <c r="B63" s="89"/>
-      <c r="C63" s="94"/>
+      <c r="A63" s="133"/>
+      <c r="B63" s="107"/>
+      <c r="C63" s="129"/>
       <c r="D63" s="68" t="s">
         <v>54</v>
       </c>
@@ -2770,9 +2770,9 @@
       <c r="I63" s="34"/>
     </row>
     <row r="64" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="99"/>
-      <c r="B64" s="89"/>
-      <c r="C64" s="95"/>
+      <c r="A64" s="133"/>
+      <c r="B64" s="107"/>
+      <c r="C64" s="92"/>
       <c r="D64" s="60" t="s">
         <v>27</v>
       </c>
@@ -2793,47 +2793,47 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="99"/>
-      <c r="B65" s="89"/>
-      <c r="C65" s="93" t="s">
+      <c r="A65" s="133"/>
+      <c r="B65" s="107"/>
+      <c r="C65" s="128" t="s">
         <v>89</v>
       </c>
       <c r="D65" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="E65" s="121" t="s">
+      <c r="E65" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="F65" s="122" t="s">
+      <c r="F65" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="G65" s="115" t="s">
+      <c r="G65" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="H65" s="115" t="s">
+      <c r="H65" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="I65" s="115" t="s">
+      <c r="I65" s="91" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="99"/>
-      <c r="B66" s="89"/>
-      <c r="C66" s="96"/>
+      <c r="A66" s="133"/>
+      <c r="B66" s="107"/>
+      <c r="C66" s="130"/>
       <c r="D66" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="E66" s="90"/>
-      <c r="F66" s="123"/>
-      <c r="G66" s="95"/>
-      <c r="H66" s="95"/>
-      <c r="I66" s="95"/>
+      <c r="E66" s="88"/>
+      <c r="F66" s="90"/>
+      <c r="G66" s="92"/>
+      <c r="H66" s="92"/>
+      <c r="I66" s="92"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="99"/>
-      <c r="B67" s="89"/>
-      <c r="C67" s="93" t="s">
+      <c r="A67" s="133"/>
+      <c r="B67" s="107"/>
+      <c r="C67" s="128" t="s">
         <v>62</v>
       </c>
       <c r="D67" s="59" t="s">
@@ -2850,9 +2850,9 @@
       <c r="I67" s="28"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="99"/>
-      <c r="B68" s="89"/>
-      <c r="C68" s="95"/>
+      <c r="A68" s="133"/>
+      <c r="B68" s="107"/>
+      <c r="C68" s="92"/>
       <c r="D68" s="73" t="s">
         <v>125</v>
       </c>
@@ -2867,9 +2867,9 @@
       <c r="I68" s="32"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="99"/>
-      <c r="B69" s="89"/>
-      <c r="C69" s="93" t="s">
+      <c r="A69" s="133"/>
+      <c r="B69" s="107"/>
+      <c r="C69" s="128" t="s">
         <v>63</v>
       </c>
       <c r="D69" s="59" t="s">
@@ -2878,7 +2878,7 @@
       <c r="E69" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="F69" s="115" t="s">
+      <c r="F69" s="91" t="s">
         <v>7</v>
       </c>
       <c r="G69" s="45"/>
@@ -2886,16 +2886,16 @@
       <c r="I69" s="32"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" s="99"/>
-      <c r="B70" s="89"/>
-      <c r="C70" s="96"/>
+      <c r="A70" s="133"/>
+      <c r="B70" s="107"/>
+      <c r="C70" s="130"/>
       <c r="D70" s="59" t="s">
         <v>128</v>
       </c>
       <c r="E70" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="F70" s="133"/>
+      <c r="F70" s="93"/>
       <c r="G70" s="45"/>
       <c r="H70" s="3"/>
       <c r="I70" s="32"/>
@@ -2912,13 +2912,13 @@
       <c r="I71" s="32"/>
     </row>
     <row r="72" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="91" t="s">
+      <c r="A72" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="B72" s="91" t="s">
+      <c r="B72" s="112" t="s">
         <v>98</v>
       </c>
-      <c r="C72" s="93" t="s">
+      <c r="C72" s="128" t="s">
         <v>99</v>
       </c>
       <c r="D72" s="55" t="s">
@@ -2935,13 +2935,13 @@
       <c r="I72" s="39"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" s="92"/>
-      <c r="B73" s="92"/>
-      <c r="C73" s="97"/>
+      <c r="A73" s="113"/>
+      <c r="B73" s="113"/>
+      <c r="C73" s="131"/>
       <c r="D73" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="E73" s="121" t="s">
+      <c r="E73" s="87" t="s">
         <v>65</v>
       </c>
       <c r="F73" s="75" t="s">
@@ -2952,13 +2952,13 @@
       <c r="I73" s="39"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="92"/>
-      <c r="B74" s="92"/>
-      <c r="C74" s="97"/>
+      <c r="A74" s="113"/>
+      <c r="B74" s="113"/>
+      <c r="C74" s="131"/>
       <c r="D74" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="E74" s="90"/>
+      <c r="E74" s="88"/>
       <c r="F74" s="54" t="s">
         <v>7</v>
       </c>
@@ -2967,9 +2967,9 @@
       <c r="I74" s="39"/>
     </row>
     <row r="75" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="89"/>
-      <c r="B75" s="89"/>
-      <c r="C75" s="93" t="s">
+      <c r="A75" s="107"/>
+      <c r="B75" s="107"/>
+      <c r="C75" s="128" t="s">
         <v>100</v>
       </c>
       <c r="D75" s="60" t="s">
@@ -2986,9 +2986,9 @@
       <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="89"/>
-      <c r="B76" s="89"/>
-      <c r="C76" s="95"/>
+      <c r="A76" s="107"/>
+      <c r="B76" s="107"/>
+      <c r="C76" s="92"/>
       <c r="D76" s="60" t="s">
         <v>74</v>
       </c>
@@ -3003,8 +3003,8 @@
       <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="89"/>
-      <c r="B77" s="89"/>
+      <c r="A77" s="107"/>
+      <c r="B77" s="107"/>
       <c r="C77" s="65" t="s">
         <v>134</v>
       </c>
@@ -3022,9 +3022,9 @@
       <c r="I77" s="49"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="89"/>
-      <c r="B78" s="89"/>
-      <c r="C78" s="93" t="s">
+      <c r="A78" s="107"/>
+      <c r="B78" s="107"/>
+      <c r="C78" s="128" t="s">
         <v>66</v>
       </c>
       <c r="D78" s="66" t="s">
@@ -3041,9 +3041,9 @@
       <c r="I78" s="49"/>
     </row>
     <row r="79" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="89"/>
-      <c r="B79" s="89"/>
-      <c r="C79" s="94"/>
+      <c r="A79" s="107"/>
+      <c r="B79" s="107"/>
+      <c r="C79" s="129"/>
       <c r="D79" s="60" t="s">
         <v>67</v>
       </c>
@@ -3058,9 +3058,9 @@
       <c r="I79" s="39"/>
     </row>
     <row r="80" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="89"/>
-      <c r="B80" s="89"/>
-      <c r="C80" s="94"/>
+      <c r="A80" s="107"/>
+      <c r="B80" s="107"/>
+      <c r="C80" s="129"/>
       <c r="D80" s="68" t="s">
         <v>135</v>
       </c>
@@ -3075,9 +3075,9 @@
       <c r="I80" s="39"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A81" s="90"/>
-      <c r="B81" s="90"/>
-      <c r="C81" s="95"/>
+      <c r="A81" s="88"/>
+      <c r="B81" s="88"/>
+      <c r="C81" s="92"/>
       <c r="D81" s="66" t="s">
         <v>68</v>
       </c>
@@ -3290,50 +3290,6 @@
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="E65:E66"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="F69:F70"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F23:F27"/>
-    <mergeCell ref="E23:E27"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="E30:E43"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E53:E55"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="A47:A58"/>
-    <mergeCell ref="B47:B58"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="A17:A29"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="C20:C27"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B6:B15"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="B30:B43"/>
-    <mergeCell ref="A30:A43"/>
-    <mergeCell ref="C34:C43"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="F34:F42"/>
-    <mergeCell ref="F30:F32"/>
     <mergeCell ref="B72:B81"/>
     <mergeCell ref="A72:A81"/>
     <mergeCell ref="C78:C81"/>
@@ -3345,8 +3301,52 @@
     <mergeCell ref="B60:B70"/>
     <mergeCell ref="C60:C64"/>
     <mergeCell ref="C65:C66"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B6:B15"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="C20:C27"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="B30:B43"/>
+    <mergeCell ref="C34:C43"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="F34:F42"/>
+    <mergeCell ref="F30:F32"/>
     <mergeCell ref="C47:C50"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E53:E55"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="A47:A58"/>
+    <mergeCell ref="B47:B58"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="A17:A29"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A30:A43"/>
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="E30:E43"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="F69:F70"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
